--- a/Horario_TV_DSL.xlsx
+++ b/Horario_TV_DSL.xlsx
@@ -41,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -63,40 +63,13 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,17 +455,6 @@
   </sheetPr>
   <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -500,626 +462,652 @@
           <t>Programacion Lunes</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Hora de inicio</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Hora de terminacion</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Tipo calc</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="3">
+      <c r="D4" s="1" t="inlineStr"/>
+      <c r="E4" s="1">
         <f>IF(G4&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1">
         <f>IF(G5&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+      <c r="I5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>REVISTA HOLA HABANA</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>revista</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" s="3">
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1">
         <f>IF(G6&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>REVISTA HOLA HABANA</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>DÉCADAS MILAGROSAS</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="4">
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1">
         <f>IF(G7&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="1">
         <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>DÉCADAS MILAGROSAS</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="3">
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1">
         <f>IF(G8&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>POWER RANGERS</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>infantil</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1">
         <f>IF(G9&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>POWER RANGERS</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>CINECITO EN TV</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" s="3">
+      <c r="D10" s="1" t="inlineStr"/>
+      <c r="E10" s="1">
         <f>IF(G10&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>CINECITO EN TV</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS INFANTILES</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="4">
+      <c r="D11" s="1" t="inlineStr"/>
+      <c r="E11" s="1">
         <f>IF(G11&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="1">
         <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS INFANTILES</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>VE Y MIRA</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" s="3">
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1">
         <f>IF(G12&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="1">
         <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>VE Y MIRA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>MÚSICA HABANA</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" s="4">
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1">
         <f>IF(G13&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="1">
         <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>MÚSICA HABANA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>HABANA COLECCIÓN</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" s="3">
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1">
         <f>IF(G14&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="1">
         <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>HABANA COLECCIÓN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>MÚSICA SÍ</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" s="4">
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1">
         <f>IF(G15&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="1">
         <f>IF(G15&lt;&gt;"",TEXT(TIMEVALUE(E15)+IFERROR(VLOOKUP(G15,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>MÚSICA SÍ</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>D DISEÑO</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" s="3">
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1">
         <f>IF(G16&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="1">
         <f>IF(G16&lt;&gt;"",TEXT(TIMEVALUE(E16)+IFERROR(VLOOKUP(G16,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>D DISEÑO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" s="1" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>SIN PUNTOS SUSPENSIVOS</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>entrevista</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" s="4">
+      <c r="D17" s="1" t="inlineStr"/>
+      <c r="E17" s="1">
         <f>IF(G17&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="1">
         <f>IF(G17&lt;&gt;"",TEXT(TIMEVALUE(E17)+IFERROR(VLOOKUP(G17,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>SIN PUNTOS SUSPENSIVOS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr"/>
+      <c r="I17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" s="3">
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1">
         <f>IF(G18&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="1">
         <f>IF(G18&lt;&gt;"",TEXT(TIMEVALUE(E18)+IFERROR(VLOOKUP(G18,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" s="4">
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1">
         <f>IF(G19&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="1">
         <f>IF(G19&lt;&gt;"",TEXT(TIMEVALUE(E19)+IFERROR(VLOOKUP(G19,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20">
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1">
         <f>IF(G20&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <f>IF(G20&lt;&gt;"",TEXT(TIMEVALUE(E20)+IFERROR(VLOOKUP(G20,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="E21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="1" t="n"/>
+      <c r="D21" s="1" t="n"/>
+      <c r="E21" s="1">
         <f>IF(G21&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <f>IF(G21&lt;&gt;"",TEXT(TIMEVALUE(E21)+IFERROR(VLOOKUP(G21,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G21" s="1" t="n"/>
+      <c r="H21" s="1" t="n"/>
+      <c r="I21" s="1" t="n"/>
     </row>
     <row r="22">
-      <c r="E22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="n"/>
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="1">
         <f>IF(G22&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <f>IF(G22&lt;&gt;"",TEXT(TIMEVALUE(E22)+IFERROR(VLOOKUP(G22,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G22" s="1" t="n"/>
+      <c r="H22" s="1" t="n"/>
+      <c r="I22" s="1" t="n"/>
     </row>
     <row r="23">
-      <c r="E23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="1" t="n"/>
+      <c r="D23" s="1" t="n"/>
+      <c r="E23" s="1">
         <f>IF(G23&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <f>IF(G23&lt;&gt;"",TEXT(TIMEVALUE(E23)+IFERROR(VLOOKUP(G23,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G23" s="1" t="n"/>
+      <c r="H23" s="1" t="n"/>
+      <c r="I23" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
   <conditionalFormatting sqref="G23">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>ISNA(MATCH(G23,$A$4:$C$20,0))</formula>
@@ -1289,17 +1277,6 @@
   </sheetPr>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1307,378 +1284,404 @@
           <t>Programacion Martes</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Hora de inicio</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Hora de terminacion</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Tipo calc</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>TODO POP</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="3">
+      <c r="D4" s="1" t="inlineStr"/>
+      <c r="E4" s="1">
         <f>IF(G4&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>TODO POP</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>BREVES ESTACIONES</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1">
         <f>IF(G5&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>BREVES ESTACIONES</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+      <c r="I5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>SALUDARTE</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>salud</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" s="3">
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1">
         <f>IF(G6&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>SALUDARTE</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>SECUENCIA</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="4">
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1">
         <f>IF(G7&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="1">
         <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>SECUENCIA</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>RITMO CLIP</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="3">
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1">
         <f>IF(G8&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>RITMO CLIP</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>TRIANGULO DE LA CONFIANZA</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>entrevista</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1">
         <f>IF(G9&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>TRIANGULO DE LA CONFIANZA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" s="3">
+      <c r="D10" s="1" t="inlineStr"/>
+      <c r="E10" s="1">
         <f>IF(G10&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="4">
+      <c r="D11" s="1" t="inlineStr"/>
+      <c r="E11" s="1">
         <f>IF(G11&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="1">
         <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12">
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1">
         <f>IF(G12&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="E13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="n"/>
+      <c r="D13" s="1" t="n"/>
+      <c r="E13" s="1">
         <f>IF(G13&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G13" s="1" t="n"/>
+      <c r="H13" s="1" t="n"/>
+      <c r="I13" s="1" t="n"/>
     </row>
     <row r="14">
-      <c r="E14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="1" t="n"/>
+      <c r="E14" s="1">
         <f>IF(G14&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G14" s="1" t="n"/>
+      <c r="H14" s="1" t="n"/>
+      <c r="I14" s="1" t="n"/>
     </row>
     <row r="15">
-      <c r="E15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="1" t="n"/>
+      <c r="E15" s="1">
         <f>IF(G15&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <f>IF(G15&lt;&gt;"",TEXT(TIMEVALUE(E15)+IFERROR(VLOOKUP(G15,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G15" s="1" t="n"/>
+      <c r="H15" s="1" t="n"/>
+      <c r="I15" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
   <conditionalFormatting sqref="G15">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>ISNA(MATCH(G15,$A$4:$C$12,0))</formula>
@@ -1784,17 +1787,6 @@
   </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1802,316 +1794,342 @@
           <t>Programacion Miercoles</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>19:45</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Hora de inicio</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Hora de terminacion</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Tipo calc</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>COSAS DEL CINE</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="3">
+      <c r="D4" s="1" t="inlineStr"/>
+      <c r="E4" s="1">
         <f>IF(G4&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>COSAS DEL CINE</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>RITMO CLIP</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1">
         <f>IF(G5&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>RITMO CLIP</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+      <c r="I5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>BANDA SONORA JUVENIL</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" s="3">
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1">
         <f>IF(G6&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>BANDA SONORA JUVENIL</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>VE Y MIRA</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="4">
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1">
         <f>IF(G7&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="1">
         <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>VE Y MIRA</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>MÚSICA DEL MUNDO</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="3">
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1">
         <f>IF(G8&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>MÚSICA DEL MUNDO</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1">
         <f>IF(G9&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>CINEMA HABANA</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10">
+      <c r="D10" s="1" t="inlineStr"/>
+      <c r="E10" s="1">
         <f>IF(G10&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>CINEMA HABANA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="E11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1">
         <f>IF(G11&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G11" s="1" t="n"/>
+      <c r="H11" s="1" t="n"/>
+      <c r="I11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="E12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1">
         <f>IF(G12&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
+      <c r="I12" s="1" t="n"/>
     </row>
     <row r="13">
-      <c r="E13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="n"/>
+      <c r="D13" s="1" t="n"/>
+      <c r="E13" s="1">
         <f>IF(G13&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G13" s="1" t="n"/>
+      <c r="H13" s="1" t="n"/>
+      <c r="I13" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
   <conditionalFormatting sqref="G13">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>ISNA(MATCH(G13,$A$4:$C$10,0))</formula>
@@ -2201,17 +2219,6 @@
   </sheetPr>
   <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -2219,657 +2226,683 @@
           <t>Programacion Jueves</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Hora de inicio</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Hora de terminacion</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Tipo calc</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="3">
+      <c r="D4" s="1" t="inlineStr"/>
+      <c r="E4" s="1">
         <f>IF(G4&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1">
         <f>IF(G5&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+      <c r="I5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>REVISTA HOLA HABANA</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>revista</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" s="3">
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1">
         <f>IF(G6&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>REVISTA HOLA HABANA</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>SALUDARTE</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>salud</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="4">
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1">
         <f>IF(G7&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="1">
         <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>SALUDARTE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>SECUENCIA</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="3">
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1">
         <f>IF(G8&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>SECUENCIA</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1">
         <f>IF(G9&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>CAZADOR DE TROLES</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>infantil</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" s="3">
+      <c r="D10" s="1" t="inlineStr"/>
+      <c r="E10" s="1">
         <f>IF(G10&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>CAZADOR DE TROLES</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>EL MUNDO DE CRAIG</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>animacion</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="4">
+      <c r="D11" s="1" t="inlineStr"/>
+      <c r="E11" s="1">
         <f>IF(G11&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="1">
         <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>EL MUNDO DE CRAIG</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>ÁNIMA</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>animacion</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" s="3">
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1">
         <f>IF(G12&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="1">
         <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>ÁNIMA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>PAPEL EN BLANCO</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" s="4">
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1">
         <f>IF(G13&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="1">
         <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>PAPEL EN BLANCO</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>MÚSICA DEL MUNDO</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" s="3">
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1">
         <f>IF(G14&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="1">
         <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>MÚSICA DEL MUNDO</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>TRAVESÍA</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" s="4">
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1">
         <f>IF(G15&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="1">
         <f>IF(G15&lt;&gt;"",TEXT(TIMEVALUE(E15)+IFERROR(VLOOKUP(G15,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>TRAVESÍA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>DONDE VA LA HABANA</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" s="3">
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1">
         <f>IF(G16&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="1">
         <f>IF(G16&lt;&gt;"",TEXT(TIMEVALUE(E16)+IFERROR(VLOOKUP(G16,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>DONDE VA LA HABANA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" s="1" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>BANDA SONORA</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" s="4">
+      <c r="D17" s="1" t="inlineStr"/>
+      <c r="E17" s="1">
         <f>IF(G17&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="1">
         <f>IF(G17&lt;&gt;"",TEXT(TIMEVALUE(E17)+IFERROR(VLOOKUP(G17,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>BANDA SONORA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr"/>
+      <c r="I17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>ESTA ES MI PEÑA</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" s="3">
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1">
         <f>IF(G18&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="1">
         <f>IF(G18&lt;&gt;"",TEXT(TIMEVALUE(E18)+IFERROR(VLOOKUP(G18,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>ESTA ES MI PEÑA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" s="4">
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1">
         <f>IF(G19&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="1">
         <f>IF(G19&lt;&gt;"",TEXT(TIMEVALUE(E19)+IFERROR(VLOOKUP(G19,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" s="2">
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1">
         <f>IF(G20&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="1">
         <f>IF(G20&lt;&gt;"",TEXT(TIMEVALUE(E20)+IFERROR(VLOOKUP(G20,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21">
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1">
         <f>IF(G21&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <f>IF(G21&lt;&gt;"",TEXT(TIMEVALUE(E21)+IFERROR(VLOOKUP(G21,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="E22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="n"/>
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="1">
         <f>IF(G22&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <f>IF(G22&lt;&gt;"",TEXT(TIMEVALUE(E22)+IFERROR(VLOOKUP(G22,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G22" s="1" t="n"/>
+      <c r="H22" s="1" t="n"/>
+      <c r="I22" s="1" t="n"/>
     </row>
     <row r="23">
-      <c r="E23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="1" t="n"/>
+      <c r="D23" s="1" t="n"/>
+      <c r="E23" s="1">
         <f>IF(G23&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <f>IF(G23&lt;&gt;"",TEXT(TIMEVALUE(E23)+IFERROR(VLOOKUP(G23,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G23" s="1" t="n"/>
+      <c r="H23" s="1" t="n"/>
+      <c r="I23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="E24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="1" t="n"/>
+      <c r="C24" s="1" t="n"/>
+      <c r="D24" s="1" t="n"/>
+      <c r="E24" s="1">
         <f>IF(G24&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <f>IF(G24&lt;&gt;"",TEXT(TIMEVALUE(E24)+IFERROR(VLOOKUP(G24,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G24" s="1" t="n"/>
+      <c r="H24" s="1" t="n"/>
+      <c r="I24" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
   <conditionalFormatting sqref="G24">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>ISNA(MATCH(G24,$A$4:$C$21,0))</formula>
@@ -3047,17 +3080,6 @@
   </sheetPr>
   <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3065,471 +3087,497 @@
           <t>Programacion Viernes</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Hora de inicio</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Hora de terminacion</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Tipo calc</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>GEN HABANERO</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>documental</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="3">
+      <c r="D4" s="1" t="inlineStr"/>
+      <c r="E4" s="1">
         <f>IF(G4&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>GEN HABANERO</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1">
         <f>IF(G5&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+      <c r="I5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>TIENE QUE VER</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" s="3">
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1">
         <f>IF(G6&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>TIENE QUE VER</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS INFANTILES</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="4">
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1">
         <f>IF(G7&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="1">
         <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS INFANTILES</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>ALGO ENTRE MANOS</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="3">
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1">
         <f>IF(G8&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>ALGO ENTRE MANOS</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>BREVES ESTACIONES</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1">
         <f>IF(G9&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>BREVES ESTACIONES</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>DÉCADAS MILAGROSAS</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" s="3">
+      <c r="D10" s="1" t="inlineStr"/>
+      <c r="E10" s="1">
         <f>IF(G10&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>DÉCADAS MILAGROSAS</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>SIN PUNTOS SUSPENSIVOS</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>entrevista</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="4">
+      <c r="D11" s="1" t="inlineStr"/>
+      <c r="E11" s="1">
         <f>IF(G11&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="1">
         <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>SIN PUNTOS SUSPENSIVOS</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>YO BAILO</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" s="3">
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1">
         <f>IF(G12&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="1">
         <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>YO BAILO</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" s="4">
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1">
         <f>IF(G13&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="1">
         <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" s="2">
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1">
         <f>IF(G14&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15">
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1">
         <f>IF(G15&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <f>IF(G15&lt;&gt;"",TEXT(TIMEVALUE(E15)+IFERROR(VLOOKUP(G15,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="E16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1">
         <f>IF(G16&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <f>IF(G16&lt;&gt;"",TEXT(TIMEVALUE(E16)+IFERROR(VLOOKUP(G16,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G16" s="1" t="n"/>
+      <c r="H16" s="1" t="n"/>
+      <c r="I16" s="1" t="n"/>
     </row>
     <row r="17">
-      <c r="E17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="n"/>
+      <c r="D17" s="1" t="n"/>
+      <c r="E17" s="1">
         <f>IF(G17&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <f>IF(G17&lt;&gt;"",TEXT(TIMEVALUE(E17)+IFERROR(VLOOKUP(G17,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G17" s="1" t="n"/>
+      <c r="H17" s="1" t="n"/>
+      <c r="I17" s="1" t="n"/>
     </row>
     <row r="18">
-      <c r="E18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1">
         <f>IF(G18&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <f>IF(G18&lt;&gt;"",TEXT(TIMEVALUE(E18)+IFERROR(VLOOKUP(G18,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G18" s="1" t="n"/>
+      <c r="H18" s="1" t="n"/>
+      <c r="I18" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
   <conditionalFormatting sqref="G18">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>ISNA(MATCH(G18,$A$4:$C$15,0))</formula>
@@ -3659,17 +3707,6 @@
   </sheetPr>
   <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3677,533 +3714,559 @@
           <t>Programacion Sabado</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Hora de inicio</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Hora de terminacion</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Tipo calc</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="3">
+      <c r="D4" s="1" t="inlineStr"/>
+      <c r="E4" s="1">
         <f>IF(G4&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1">
         <f>IF(G5&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+      <c r="I5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>CUENTAS VERDE LIMÓN</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>infantil</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" s="3">
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1">
         <f>IF(G6&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>CUENTAS VERDE LIMÓN</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>BANDA SONORA JUVENIL</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="4">
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1">
         <f>IF(G7&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="1">
         <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>BANDA SONORA JUVENIL</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>TRAVESÍA</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="3">
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1">
         <f>IF(G8&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>TRAVESÍA</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>TODO POP</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1">
         <f>IF(G9&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>TODO POP</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>SERIE JUVENIL “SABRINA, LA BRUJA ADOLESCENTE”</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" s="3">
+      <c r="D10" s="1" t="inlineStr"/>
+      <c r="E10" s="1">
         <f>IF(G10&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>SERIE JUVENIL “SABRINA, LA BRUJA ADOLESCENTE”</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>LIBRE ACCESO</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="4">
+      <c r="D11" s="1" t="inlineStr"/>
+      <c r="E11" s="1">
         <f>IF(G11&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="1">
         <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>LIBRE ACCESO</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>JUGADA PERFECTA</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>deporte</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" s="3">
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1">
         <f>IF(G12&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="1">
         <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>JUGADA PERFECTA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>QUE LA MÚSICA NO FALTE</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" s="4">
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1">
         <f>IF(G13&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="1">
         <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>QUE LA MÚSICA NO FALTE</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>COSAS DEL CINE</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" s="3">
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1">
         <f>IF(G14&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="1">
         <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>COSAS DEL CINE</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>MÚSICA HABANA</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" s="4">
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1">
         <f>IF(G15&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="1">
         <f>IF(G15&lt;&gt;"",TEXT(TIMEVALUE(E15)+IFERROR(VLOOKUP(G15,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>MÚSICA HABANA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>X DISTANTE</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>animacion</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" s="2">
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1">
         <f>IF(G16&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <f>IF(G16&lt;&gt;"",TEXT(TIMEVALUE(E16)+IFERROR(VLOOKUP(G16,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>X DISTANTE</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" s="1" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>MÚSICA SI</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17">
+      <c r="D17" s="1" t="inlineStr"/>
+      <c r="E17" s="1">
         <f>IF(G17&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <f>IF(G17&lt;&gt;"",TEXT(TIMEVALUE(E17)+IFERROR(VLOOKUP(G17,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>MÚSICA SI</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr"/>
+      <c r="I17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="E18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1">
         <f>IF(G18&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <f>IF(G18&lt;&gt;"",TEXT(TIMEVALUE(E18)+IFERROR(VLOOKUP(G18,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G18" s="1" t="n"/>
+      <c r="H18" s="1" t="n"/>
+      <c r="I18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="E19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="n"/>
+      <c r="D19" s="1" t="n"/>
+      <c r="E19" s="1">
         <f>IF(G19&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <f>IF(G19&lt;&gt;"",TEXT(TIMEVALUE(E19)+IFERROR(VLOOKUP(G19,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G19" s="1" t="n"/>
+      <c r="H19" s="1" t="n"/>
+      <c r="I19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="E20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="1" t="n"/>
+      <c r="D20" s="1" t="n"/>
+      <c r="E20" s="1">
         <f>IF(G20&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <f>IF(G20&lt;&gt;"",TEXT(TIMEVALUE(E20)+IFERROR(VLOOKUP(G20,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G20" s="1" t="n"/>
+      <c r="H20" s="1" t="n"/>
+      <c r="I20" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
   <conditionalFormatting sqref="G20">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>ISNA(MATCH(G20,$A$4:$C$17,0))</formula>
@@ -4349,17 +4412,6 @@
   </sheetPr>
   <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -4367,440 +4419,466 @@
           <t>Programacion Domingo</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Hora de inicio</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Hora de terminacion</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Tipo calc</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="3">
+      <c r="D4" s="1" t="inlineStr"/>
+      <c r="E4" s="1">
         <f>IF(G4&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1">
         <f>IF(G5&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+      <c r="I5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>CANAL HABANA DEPORTES</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="1" t="n">
         <v>890</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>deporte</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" s="3">
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1">
         <f>IF(G6&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>CANAL HABANA DEPORTES</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>LATINOS</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="4">
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1">
         <f>IF(G7&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="1">
         <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>LATINOS</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>PAPEL EN BLANCO</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="3">
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1">
         <f>IF(G8&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>PAPEL EN BLANCO</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>ALGO ENTRE MANOS</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1">
         <f>IF(G9&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="1">
         <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>ALGO ENTRE MANOS</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>VERDE HABANA</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>documental</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" s="3">
+      <c r="D10" s="1" t="inlineStr"/>
+      <c r="E10" s="1">
         <f>IF(G10&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>VERDE HABANA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>GEN HABANERO</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>documental</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="4">
+      <c r="D11" s="1" t="inlineStr"/>
+      <c r="E11" s="1">
         <f>IF(G11&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="1">
         <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>GEN HABANERO</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>TRIANGULO DE LA CONFIANZA</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>entrevista</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" s="3">
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1">
         <f>IF(G12&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="1">
         <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>TRIANGULO DE LA CONFIANZA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>BANDA SONORA</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" s="4">
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1">
         <f>IF(G13&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="1">
         <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>BANDA SONORA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>CINE +</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="1" t="n">
         <v>205</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14">
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1">
         <f>IF(G14&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>CINE +</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="E15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="1" t="n"/>
+      <c r="E15" s="1">
         <f>IF(G15&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <f>IF(G15&lt;&gt;"",TEXT(TIMEVALUE(E15)+IFERROR(VLOOKUP(G15,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G15" s="1" t="n"/>
+      <c r="H15" s="1" t="n"/>
+      <c r="I15" s="1" t="n"/>
     </row>
     <row r="16">
-      <c r="E16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1">
         <f>IF(G16&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <f>IF(G16&lt;&gt;"",TEXT(TIMEVALUE(E16)+IFERROR(VLOOKUP(G16,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G16" s="1" t="n"/>
+      <c r="H16" s="1" t="n"/>
+      <c r="I16" s="1" t="n"/>
     </row>
     <row r="17">
-      <c r="E17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="n"/>
+      <c r="D17" s="1" t="n"/>
+      <c r="E17" s="1">
         <f>IF(G17&lt;&gt;"",IF(ROW()=4,$I$2,F(PREVIOUS-ROW (HORA-FINAL))),"")</f>
         <v/>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <f>IF(G17&lt;&gt;"",TEXT(TIMEVALUE(E17)+IFERROR(VLOOKUP(G17,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
         <v/>
       </c>
+      <c r="G17" s="1" t="n"/>
+      <c r="H17" s="1" t="n"/>
+      <c r="I17" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
   <conditionalFormatting sqref="G17">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>ISNA(MATCH(G17,$A$4:$C$14,0))</formula>
@@ -4933,225 +5011,225 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Día</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Programas</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Inicio</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fin</t>
         </is>
       </c>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>480</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>270</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>242</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>19:45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>23:47</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>480</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="1" t="n">
         <v>450</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Sabado</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="1" t="n">
         <v>480</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="1" t="n">
         <v>1315</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>23:55</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="1" t="n">
         <v>3717</v>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr"/>
+      <c r="F9" s="1" t="inlineStr"/>
+      <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Canal Habana</t>
